--- a/public/templates/Code_on_Wages/Form I - Register of Fines.xlsx
+++ b/public/templates/Code_on_Wages/Form I - Register of Fines.xlsx
@@ -266,7 +266,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,19 +288,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFEBF3FB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF3FB"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFEBF3FB"/>
+        <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -360,7 +348,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -397,6 +385,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -417,23 +409,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -474,8 +466,8 @@
       <rgbColor rgb="FF7F7F7F"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFEBF3FB"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -697,7 +689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.57"/>
@@ -851,245 +843,281 @@
         <v>27</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+    </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="N11" s="13" t="s">
+      <c r="N11" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="O11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="P11" s="12" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="12"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="18"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+    <row r="12" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="16"/>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="16"/>
+    </row>
+    <row r="14" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="16"/>
+    </row>
+    <row r="15" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="16"/>
+    </row>
+    <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="16"/>
+    </row>
+    <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="19"/>
+    </row>
+    <row r="18" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K23" s="6" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F24" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K24" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F25" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K25" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F26" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K26" s="21" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1102,8 +1130,8 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A19:P19"/>
     <mergeCell ref="A20:P20"/>
+    <mergeCell ref="A21:P21"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
